--- a/data/EVA_water_samples.xlsx
+++ b/data/EVA_water_samples.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malte.willmes\Dropbox\NINA\Research\PinkPilot\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malte.willmes\Dropbox\NINA\Research\PinkPilot\manuscript\GeneticsGeochemPinkSalmonDispersal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394921B4-2056-41E6-AAED-8FF08AE0BC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0510954-A7AF-4F89-9FF1-FEDB5F542230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A914CBEC-C106-46F8-9DDC-F289FEFBC14A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A914CBEC-C106-46F8-9DDC-F289FEFBC14A}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -362,9 +362,6 @@
     <t>At the pink salmon trap.</t>
   </si>
   <si>
-    <t>Julaelva in Tanafj.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relatively small river in Tanafjorden, likely not much pink salmon there, too small and too shallow. Did not see any pink salmon. </t>
   </si>
   <si>
@@ -462,6 +459,9 @@
   </si>
   <si>
     <t>Order_ID</t>
+  </si>
+  <si>
+    <t>Julelva in Tanafj.</t>
   </si>
 </sst>
 </file>
@@ -891,7 +891,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>63</v>
@@ -906,7 +906,7 @@
         <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>66</v>
@@ -927,10 +927,10 @@
         <v>71</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>72</v>
@@ -1796,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="H20" t="s">
         <v>75</v>
@@ -1820,7 +1820,7 @@
         <v>28.489578000000002</v>
       </c>
       <c r="O20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P20" t="s">
         <v>79</v>
@@ -1843,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H21" t="s">
         <v>81</v>
@@ -1867,7 +1867,7 @@
         <v>28.054082999999999</v>
       </c>
       <c r="O21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P21" t="s">
         <v>79</v>
@@ -1890,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H22" t="s">
         <v>75</v>
@@ -1914,7 +1914,7 @@
         <v>27.836501999999999</v>
       </c>
       <c r="O22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P22" t="s">
         <v>79</v>
@@ -1937,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H23" t="s">
         <v>81</v>
@@ -1961,7 +1961,7 @@
         <v>26.336621000000001</v>
       </c>
       <c r="O23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P23" t="s">
         <v>79</v>
@@ -1984,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H24" t="s">
         <v>81</v>
@@ -2008,7 +2008,7 @@
         <v>25.571722000000001</v>
       </c>
       <c r="O24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P24" t="s">
         <v>79</v>
@@ -2031,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H25" t="s">
         <v>75</v>
@@ -2055,7 +2055,7 @@
         <v>25.251045999999999</v>
       </c>
       <c r="O25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P25" t="s">
         <v>79</v>
@@ -2078,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H26" t="s">
         <v>75</v>
@@ -2102,7 +2102,7 @@
         <v>25.032928999999999</v>
       </c>
       <c r="O26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P26" t="s">
         <v>79</v>
@@ -2125,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H27" t="s">
         <v>81</v>
@@ -2149,7 +2149,7 @@
         <v>24.905201000000002</v>
       </c>
       <c r="O27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P27" t="s">
         <v>79</v>
@@ -2172,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H28" t="s">
         <v>81</v>
@@ -2196,7 +2196,7 @@
         <v>24.348738999999998</v>
       </c>
       <c r="O28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P28" t="s">
         <v>79</v>
@@ -2219,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H29" t="s">
         <v>75</v>
@@ -2243,7 +2243,7 @@
         <v>25.072870999999999</v>
       </c>
       <c r="O29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P29" t="s">
         <v>79</v>
@@ -2266,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H30" t="s">
         <v>81</v>
@@ -2290,7 +2290,7 @@
         <v>25.047599999999999</v>
       </c>
       <c r="O30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P30" t="s">
         <v>79</v>
@@ -2313,7 +2313,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H31" t="s">
         <v>81</v>
@@ -2337,7 +2337,7 @@
         <v>24.936793999999999</v>
       </c>
       <c r="O31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P31" t="s">
         <v>79</v>
@@ -2384,7 +2384,7 @@
         <v>27.628147999999999</v>
       </c>
       <c r="O32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P32" t="s">
         <v>79</v>
@@ -2407,7 +2407,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H33" t="s">
         <v>75</v>
@@ -2431,7 +2431,7 @@
         <v>28.841429999999999</v>
       </c>
       <c r="O33" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P33" t="s">
         <v>79</v>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H34" t="s">
         <v>81</v>
@@ -2478,7 +2478,7 @@
         <v>29.459181000000001</v>
       </c>
       <c r="O34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P34" t="s">
         <v>79</v>
@@ -2501,7 +2501,7 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H35" t="s">
         <v>81</v>
@@ -2525,7 +2525,7 @@
         <v>29.374251999999998</v>
       </c>
       <c r="O35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P35" t="s">
         <v>79</v>
